--- a/prix/lambris.xlsx
+++ b/prix/lambris.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lambris\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lambris\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172F69D7-3933-436F-A1F7-69FED6FB9F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F023C91-78E5-44C8-9C25-70C6BB20D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>path</t>
   </si>
@@ -102,6 +102,21 @@
   </si>
   <si>
     <t>726158</t>
+  </si>
+  <si>
+    <t>galerie/millim.jpg</t>
+  </si>
+  <si>
+    <t>galerie/cristo.jpg</t>
+  </si>
+  <si>
+    <t>galerie/sarezzi.jpg</t>
+  </si>
+  <si>
+    <t>galerie/blanc-sat.jpg</t>
+  </si>
+  <si>
+    <t>galerie/blanc-brillant.jpg</t>
   </si>
 </sst>
 </file>
@@ -613,7 +628,9 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
+      <c r="A2" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="B2" s="21" t="s">
         <v>13</v>
       </c>
@@ -634,7 +651,9 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
+      <c r="A3" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="B3" s="21" t="s">
         <v>14</v>
       </c>
@@ -655,7 +674,9 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
+      <c r="A4" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="B4" s="21" t="s">
         <v>15</v>
       </c>
@@ -676,7 +697,9 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="B5" s="21" t="s">
         <v>16</v>
       </c>
@@ -697,7 +720,9 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="B6" s="21" t="s">
         <v>17</v>
       </c>

--- a/prix/lambris.xlsx
+++ b/prix/lambris.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lambris\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lambris\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F023C91-78E5-44C8-9C25-70C6BB20D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25515BF7-7FD1-43DB-9AE7-270D82267FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -245,19 +245,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -631,22 +619,22 @@
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="12">
         <v>15</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="23">
-        <v>91.021000000006609</v>
-      </c>
-      <c r="G2" s="24" t="s">
+      <c r="F2" s="20">
+        <v>36.969000000006602</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -654,22 +642,22 @@
       <c r="A3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="12">
         <v>15</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="20">
         <v>125.46600000000014</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -677,22 +665,22 @@
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="12">
         <v>15</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="20">
         <v>78.721999999996953</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -700,22 +688,22 @@
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="12">
         <v>15</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="20">
         <v>84.876000000000431</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -723,22 +711,22 @@
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="12">
         <v>26.18</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="20">
         <v>93.057999999999993</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="8" t="s">
         <v>21</v>
       </c>
     </row>

--- a/prix/lambris.xlsx
+++ b/prix/lambris.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lambris\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25515BF7-7FD1-43DB-9AE7-270D82267FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6E0D5E-A1AB-4E72-B3B7-CE390136D4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -244,6 +244,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -625,14 +628,14 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="20">
         <v>15</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="20">
-        <v>36.969000000006602</v>
+      <c r="F2" s="21">
+        <v>100.86900000000659</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>6</v>
@@ -648,13 +651,13 @@
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="20">
         <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="21">
         <v>125.46600000000014</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -671,13 +674,13 @@
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="20">
         <v>15</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>78.721999999996953</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -694,14 +697,14 @@
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="20">
         <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="20">
-        <v>84.876000000000431</v>
+      <c r="F5" s="21">
+        <v>82.419000000000437</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>20</v>
@@ -717,13 +720,13 @@
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="20">
         <v>26.18</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>93.057999999999993</v>
       </c>
       <c r="G6" s="8" t="s">
